--- a/InputData/trans/BNoEVC/BAU Number of EV Chargers.xlsx
+++ b/InputData/trans/BNoEVC/BAU Number of EV Chargers.xlsx
@@ -1,25 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26327"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\trans\BNoEVC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\trans\BRAaCTSC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FEBD4AD-B914-4E0D-A747-F65D9ED3E01E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EAF56AC-016E-492C-8470-28F213A73717}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20" yWindow="520" windowWidth="19180" windowHeight="10180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="BNoEVC" sheetId="3" r:id="rId2"/>
+    <sheet name="IIJA" sheetId="5" r:id="rId2"/>
+    <sheet name="Inflation Reduction Act" sheetId="6" r:id="rId3"/>
+    <sheet name="Calculations" sheetId="4" r:id="rId4"/>
+    <sheet name="BNoEVC" sheetId="3" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="income">#REF!</definedName>
-    <definedName name="Range_EV">#REF!</definedName>
-    <definedName name="range_ICE">#REF!</definedName>
+    <definedName name="income">Calculations!#REF!</definedName>
+    <definedName name="Range_EV">Calculations!#REF!</definedName>
+    <definedName name="range_ICE">Calculations!#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -62,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
   <si>
     <t>Source:</t>
   </si>
@@ -70,47 +73,156 @@
     <t>Notes</t>
   </si>
   <si>
+    <t>2019 to 2012 USD</t>
+  </si>
+  <si>
+    <t>Number of gas pumps</t>
+  </si>
+  <si>
+    <t>Number of Gas pumps</t>
+  </si>
+  <si>
+    <t>CleanTechnica</t>
+  </si>
+  <si>
+    <t>Stop Comparing the Number of Gas Stations to EV Charging Stations</t>
+  </si>
+  <si>
+    <t>Number of EVSE Ports</t>
+  </si>
+  <si>
+    <t>Alternative Fuels Data Center</t>
+  </si>
+  <si>
+    <t>Electric Vehicle Charging Station Locations</t>
+  </si>
+  <si>
+    <t>https://cleantechnica.com/2018/03/07/stop-comparing-number-gas-stations-ev-charging-stations/</t>
+  </si>
+  <si>
+    <t>Currency Conversion</t>
+  </si>
+  <si>
+    <t>We assume EV charger additions based on investments in the Infrastructure Investment and Jobs Act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total government funding: </t>
+  </si>
+  <si>
+    <t>($7.5 billion between 2022 and 2026), assuming 80% of the costs are paid for by the government.</t>
+  </si>
+  <si>
+    <t>Total government + private funding:</t>
+  </si>
+  <si>
+    <t>Average weighted charger cost (see trans/EVCC):</t>
+  </si>
+  <si>
+    <t>Methodology:</t>
+  </si>
+  <si>
+    <t>Calculations:</t>
+  </si>
+  <si>
+    <t>Alternative fuel refueling property credit amount</t>
+  </si>
+  <si>
+    <t>Assumed Amount of Spending Directed Toward Public LDV Chargers</t>
+  </si>
+  <si>
+    <t>Number of Chargers Added</t>
+  </si>
+  <si>
+    <t>Chargers Added by 2032</t>
+  </si>
+  <si>
+    <t>We calculate an incremental number of chargers deployed based on funding in the Inflation Reduction Act and the model's weighted average charger cost. We take estimated funding from the released JCT scores and assume 80% of the spending is directed toward public chargers. We do not attempt to model the effects of private chargers. The number of additional chargers is then fed into the shadow price used to represent range/charging anxiety for passenger LDV owners, which is partially determined by the ratio of charging infrastructure to gasoline pumps. This adjustment helps to drop the shadow price in response to additional infrastructure and increase consumer adoption of electric vehicles.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri, sans-serif"/>
+      </rPr>
+      <t xml:space="preserve">Source: </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri, sans-serif"/>
+      </rPr>
+      <t>https://www.jct.gov/publications/2022/jcx-18-22/</t>
+    </r>
+  </si>
+  <si>
+    <t>EPS Weighted Avg Charger Cost (see trans/EVCC):</t>
+  </si>
+  <si>
+    <t>2022 to 2012 $</t>
+  </si>
+  <si>
+    <t>JCT Estimates for Alternative fuel refueling property credit (million 2022$)</t>
+  </si>
+  <si>
+    <t>Assumed Number of EVSE ports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">We adjust our calculations by an estimated number of public charger additions from both the Infrastructure Investment and Jobs Act </t>
+  </si>
+  <si>
+    <t>and the Inflation Reduction Act (see tabs for methodology).</t>
+  </si>
+  <si>
+    <t>Government Outlays After Transferability Multiplier of 7.5%</t>
+  </si>
+  <si>
     <t>Number of chargers</t>
   </si>
   <si>
     <t>BAU EV Chargers</t>
   </si>
   <si>
+    <t>Pre-IIJA and IRA Assumption, Number of Chargers</t>
+  </si>
+  <si>
+    <t>IIJA Additional Chargers</t>
+  </si>
+  <si>
+    <t>IRA Additional Chargers</t>
+  </si>
+  <si>
+    <t>Total funding in 2012 $</t>
+  </si>
+  <si>
+    <t>2022 to 2012 USD</t>
+  </si>
+  <si>
+    <t>2021 to 2012 USD</t>
+  </si>
+  <si>
+    <t>Number of Chargers with IIJA and IRA Additions</t>
+  </si>
+  <si>
     <t>BNoEVC BAU Number of EV Chargers</t>
   </si>
   <si>
-    <t>https://driveelectric.gov/stations-growth</t>
-  </si>
-  <si>
-    <t>Joint Office of Energy and Transportation</t>
-  </si>
-  <si>
-    <t>Electric Vehicle Chargign Infrastructure Growth</t>
-  </si>
-  <si>
-    <t>Number of EVSE Ports, Historical</t>
-  </si>
-  <si>
-    <t>Used December data for years 2024 and 2025</t>
-  </si>
-  <si>
-    <t>Lacking reliable projections, we assume a constant growth rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">for EV charging infrastructure additions through 2050. This comes close </t>
-  </si>
-  <si>
-    <t>to equaling the number of gas station pumps by the year 2050, which</t>
-  </si>
-  <si>
-    <t>would nearly eliminate charging anxiety by 2050.</t>
+    <t>https://afdc.energy.gov/fuels/electricity_locations.html#/analyze?fuel=ELEC&amp;country=US</t>
+  </si>
+  <si>
+    <t>Annual chargers added through 2026</t>
+  </si>
+  <si>
+    <t>We assume that prior to the IIJA or IRA, the number of EV ports would slowly grow with time to equal the number of gas pumps by 2050.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -154,8 +266,40 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri, sans-serif"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF1155CC"/>
+      <name val="Calibri, sans-serif"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri, sans-serif"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -166,6 +310,12 @@
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCFE2F3"/>
+        <bgColor rgb="FFCFE2F3"/>
       </patternFill>
     </fill>
   </fills>
@@ -183,7 +333,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -195,8 +345,30 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -479,78 +651,123 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B23"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16.54296875" customWidth="1"/>
-    <col min="2" max="2" width="31.81640625" customWidth="1"/>
+    <col min="1" max="1" width="16.5703125" customWidth="1"/>
+    <col min="2" max="2" width="31.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="4" t="s">
+    <row r="4" spans="1:2">
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="B5" s="5">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="B7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="B9" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="B10" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B5" s="5">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B7" s="6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B8" t="s">
+    <row r="11" spans="1:2">
+      <c r="B11" s="5">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="B12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" s="1" t="s">
+    <row r="13" spans="1:2">
+      <c r="B13" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A14" s="7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A15" s="8"/>
+      <c r="B16">
+        <v>0.89805481563188172</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>2</v>
+      </c>
+      <c r="B17">
+        <v>0.84730412960844359</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="14">
+        <v>0.78500000000000003</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="14"/>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="15"/>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
+        <v>30</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -559,215 +776,1896 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5D98A39-3A78-451F-9516-0CF8624C92E2}">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="29.140625" customWidth="1"/>
+    <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4">
+        <v>7500000000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="30">
+      <c r="A5" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5">
+        <f>B4/0.8</f>
+        <v>9375000000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6">
+        <f>B5*About!B17</f>
+        <v>7943476215.0791588</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="30">
+      <c r="A8" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8">
+        <v>24443</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="30">
+      <c r="A10" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" s="2">
+        <f>B6/B8/5</f>
+        <v>64995.918791303513</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B7347CE-ACDC-4498-BA24-2581FCABA72A}">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
+  <dimension ref="A1:AL24"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="60.7109375" style="10" customWidth="1"/>
+    <col min="2" max="2" width="27.42578125" style="10" customWidth="1"/>
+    <col min="3" max="3" width="17.85546875" style="10" customWidth="1"/>
+    <col min="4" max="4" width="18.140625" style="10" customWidth="1"/>
+    <col min="5" max="6" width="16.140625" style="10" customWidth="1"/>
+    <col min="7" max="11" width="12.5703125" style="10"/>
+    <col min="12" max="12" width="16.42578125" style="10" customWidth="1"/>
+    <col min="13" max="16384" width="12.5703125" style="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:38" ht="14.25" customHeight="1">
+      <c r="A1" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="9"/>
+      <c r="Z1" s="9"/>
+      <c r="AA1" s="9"/>
+      <c r="AB1" s="9"/>
+      <c r="AC1" s="9"/>
+      <c r="AD1" s="9"/>
+      <c r="AE1" s="9"/>
+      <c r="AF1" s="9"/>
+      <c r="AG1" s="9"/>
+      <c r="AH1" s="9"/>
+      <c r="AI1" s="9"/>
+      <c r="AJ1" s="9"/>
+      <c r="AK1" s="9"/>
+      <c r="AL1" s="9"/>
+    </row>
+    <row r="2" spans="1:38" ht="180">
+      <c r="A2" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12"/>
+    </row>
+    <row r="3" spans="1:38" ht="14.25" customHeight="1">
+      <c r="A3" s="12"/>
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="14"/>
+      <c r="L3" s="14"/>
+      <c r="M3" s="14"/>
+      <c r="N3" s="14"/>
+      <c r="O3" s="14"/>
+      <c r="P3" s="14"/>
+      <c r="Q3" s="14"/>
+      <c r="R3" s="14"/>
+      <c r="S3" s="14"/>
+      <c r="T3" s="14"/>
+      <c r="U3" s="14"/>
+      <c r="V3" s="14"/>
+      <c r="W3" s="14"/>
+      <c r="X3" s="14"/>
+      <c r="Y3" s="14"/>
+      <c r="Z3" s="14"/>
+      <c r="AA3" s="14"/>
+      <c r="AB3" s="14"/>
+      <c r="AC3" s="14"/>
+      <c r="AD3" s="14"/>
+      <c r="AE3" s="14"/>
+      <c r="AF3" s="14"/>
+      <c r="AG3" s="14"/>
+      <c r="AH3" s="14"/>
+      <c r="AI3" s="14"/>
+      <c r="AJ3" s="14"/>
+      <c r="AK3" s="14"/>
+      <c r="AL3" s="14"/>
+    </row>
+    <row r="4" spans="1:38" ht="14.25" customHeight="1">
+      <c r="A4" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
+      <c r="N4" s="14"/>
+      <c r="O4" s="14"/>
+      <c r="P4" s="14"/>
+      <c r="Q4" s="14"/>
+      <c r="R4" s="14"/>
+      <c r="S4" s="14"/>
+      <c r="T4" s="14"/>
+      <c r="U4" s="14"/>
+      <c r="V4" s="14"/>
+      <c r="W4" s="14"/>
+      <c r="X4" s="14"/>
+      <c r="Y4" s="14"/>
+      <c r="Z4" s="14"/>
+      <c r="AA4" s="14"/>
+      <c r="AB4" s="14"/>
+      <c r="AC4" s="14"/>
+      <c r="AD4" s="14"/>
+      <c r="AE4" s="14"/>
+      <c r="AF4" s="14"/>
+      <c r="AG4" s="14"/>
+      <c r="AH4" s="14"/>
+      <c r="AI4" s="14"/>
+      <c r="AJ4" s="14"/>
+      <c r="AK4" s="14"/>
+      <c r="AL4" s="14"/>
+    </row>
+    <row r="5" spans="1:38" ht="14.25" customHeight="1">
+      <c r="A5" s="12"/>
+      <c r="B5" s="14"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="14"/>
+      <c r="J5" s="14"/>
+      <c r="K5" s="14"/>
+      <c r="L5" s="14"/>
+      <c r="M5" s="14"/>
+      <c r="N5" s="14"/>
+      <c r="O5" s="14"/>
+      <c r="P5" s="14"/>
+      <c r="Q5" s="14"/>
+      <c r="R5" s="14"/>
+      <c r="S5" s="14"/>
+      <c r="T5" s="14"/>
+      <c r="U5" s="14"/>
+      <c r="V5" s="14"/>
+      <c r="W5" s="14"/>
+      <c r="X5" s="14"/>
+      <c r="Y5" s="14"/>
+      <c r="Z5" s="14"/>
+      <c r="AA5" s="14"/>
+      <c r="AB5" s="14"/>
+      <c r="AC5" s="14"/>
+      <c r="AD5" s="14"/>
+      <c r="AE5" s="14"/>
+      <c r="AF5" s="14"/>
+      <c r="AG5" s="14"/>
+      <c r="AH5" s="14"/>
+      <c r="AI5" s="14"/>
+      <c r="AJ5" s="14"/>
+      <c r="AK5" s="14"/>
+      <c r="AL5" s="14"/>
+    </row>
+    <row r="6" spans="1:38" ht="14.25" customHeight="1">
+      <c r="A6" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="9"/>
+      <c r="M6" s="9"/>
+      <c r="N6" s="9"/>
+      <c r="O6" s="9"/>
+      <c r="P6" s="9"/>
+      <c r="Q6" s="9"/>
+      <c r="R6" s="9"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="9"/>
+      <c r="U6" s="9"/>
+      <c r="V6" s="9"/>
+      <c r="W6" s="9"/>
+      <c r="X6" s="9"/>
+      <c r="Y6" s="9"/>
+      <c r="Z6" s="9"/>
+      <c r="AA6" s="9"/>
+      <c r="AB6" s="9"/>
+      <c r="AC6" s="9"/>
+      <c r="AD6" s="9"/>
+      <c r="AE6" s="9"/>
+      <c r="AF6" s="9"/>
+      <c r="AG6" s="9"/>
+      <c r="AH6" s="9"/>
+      <c r="AI6" s="9"/>
+      <c r="AJ6" s="9"/>
+      <c r="AK6" s="9"/>
+      <c r="AL6" s="9"/>
+    </row>
+    <row r="7" spans="1:38" ht="15">
+      <c r="A7" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="14">
+        <v>24443</v>
+      </c>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="12"/>
+      <c r="L7" s="12"/>
+    </row>
+    <row r="8" spans="1:38" ht="15">
+      <c r="A8" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="14">
+        <v>0.78500000000000003</v>
+      </c>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="12"/>
+      <c r="L8" s="12"/>
+    </row>
+    <row r="9" spans="1:38" ht="15">
+      <c r="A9" s="12"/>
+      <c r="B9" s="12"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="12"/>
+      <c r="K9" s="12"/>
+      <c r="L9" s="12"/>
+    </row>
+    <row r="10" spans="1:38" ht="15">
+      <c r="A10" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="18">
+        <v>0.3</v>
+      </c>
+      <c r="C10" s="15"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="15"/>
+      <c r="M10" s="16"/>
+      <c r="N10" s="16"/>
+      <c r="O10" s="16"/>
+      <c r="P10" s="16"/>
+      <c r="Q10" s="16"/>
+      <c r="R10" s="16"/>
+      <c r="S10" s="16"/>
+      <c r="T10" s="16"/>
+      <c r="U10" s="16"/>
+      <c r="V10" s="16"/>
+      <c r="W10" s="16"/>
+      <c r="X10" s="16"/>
+      <c r="Y10" s="16"/>
+      <c r="Z10" s="16"/>
+      <c r="AA10" s="16"/>
+      <c r="AB10" s="16"/>
+      <c r="AC10" s="16"/>
+      <c r="AD10" s="16"/>
+      <c r="AE10" s="16"/>
+      <c r="AF10" s="16"/>
+      <c r="AG10" s="16"/>
+      <c r="AH10" s="16"/>
+      <c r="AI10" s="16"/>
+      <c r="AJ10" s="16"/>
+      <c r="AK10" s="16"/>
+      <c r="AL10" s="16"/>
+    </row>
+    <row r="11" spans="1:38" ht="15">
+      <c r="A11" s="15"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="15"/>
+      <c r="I11" s="15"/>
+      <c r="J11" s="15"/>
+      <c r="K11" s="15"/>
+      <c r="L11" s="15"/>
+      <c r="M11" s="16"/>
+      <c r="N11" s="16"/>
+      <c r="O11" s="16"/>
+      <c r="P11" s="16"/>
+      <c r="Q11" s="16"/>
+      <c r="R11" s="16"/>
+      <c r="S11" s="16"/>
+      <c r="T11" s="16"/>
+      <c r="U11" s="16"/>
+      <c r="V11" s="16"/>
+      <c r="W11" s="16"/>
+      <c r="X11" s="16"/>
+      <c r="Y11" s="16"/>
+      <c r="Z11" s="16"/>
+      <c r="AA11" s="16"/>
+      <c r="AB11" s="16"/>
+      <c r="AC11" s="16"/>
+      <c r="AD11" s="16"/>
+      <c r="AE11" s="16"/>
+      <c r="AF11" s="16"/>
+      <c r="AG11" s="16"/>
+      <c r="AH11" s="16"/>
+      <c r="AI11" s="16"/>
+      <c r="AJ11" s="16"/>
+      <c r="AK11" s="16"/>
+      <c r="AL11" s="16"/>
+    </row>
+    <row r="12" spans="1:38" ht="30">
+      <c r="A12" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="18">
+        <v>0.8</v>
+      </c>
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="15"/>
+      <c r="J12" s="15"/>
+      <c r="K12" s="15"/>
+      <c r="L12" s="15"/>
+      <c r="M12" s="16"/>
+      <c r="N12" s="16"/>
+      <c r="O12" s="16"/>
+      <c r="P12" s="16"/>
+      <c r="Q12" s="16"/>
+      <c r="R12" s="16"/>
+      <c r="S12" s="16"/>
+      <c r="T12" s="16"/>
+      <c r="U12" s="16"/>
+      <c r="V12" s="16"/>
+      <c r="W12" s="16"/>
+      <c r="X12" s="16"/>
+      <c r="Y12" s="16"/>
+      <c r="Z12" s="16"/>
+      <c r="AA12" s="16"/>
+      <c r="AB12" s="16"/>
+      <c r="AC12" s="16"/>
+      <c r="AD12" s="16"/>
+      <c r="AE12" s="16"/>
+      <c r="AF12" s="16"/>
+      <c r="AG12" s="16"/>
+      <c r="AH12" s="16"/>
+      <c r="AI12" s="16"/>
+      <c r="AJ12" s="16"/>
+      <c r="AK12" s="16"/>
+      <c r="AL12" s="16"/>
+    </row>
+    <row r="13" spans="1:38" ht="15">
+      <c r="A13" s="15"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="15"/>
+      <c r="J13" s="15"/>
+      <c r="K13" s="15"/>
+      <c r="L13" s="15"/>
+      <c r="M13" s="16"/>
+      <c r="N13" s="16"/>
+      <c r="O13" s="16"/>
+      <c r="P13" s="16"/>
+      <c r="Q13" s="16"/>
+      <c r="R13" s="16"/>
+      <c r="S13" s="16"/>
+      <c r="T13" s="16"/>
+      <c r="U13" s="16"/>
+      <c r="V13" s="16"/>
+      <c r="W13" s="16"/>
+      <c r="X13" s="16"/>
+      <c r="Y13" s="16"/>
+      <c r="Z13" s="16"/>
+      <c r="AA13" s="16"/>
+      <c r="AB13" s="16"/>
+      <c r="AC13" s="16"/>
+      <c r="AD13" s="16"/>
+      <c r="AE13" s="16"/>
+      <c r="AF13" s="16"/>
+      <c r="AG13" s="16"/>
+      <c r="AH13" s="16"/>
+      <c r="AI13" s="16"/>
+      <c r="AJ13" s="16"/>
+      <c r="AK13" s="16"/>
+      <c r="AL13" s="16"/>
+    </row>
+    <row r="14" spans="1:38" ht="15">
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="15"/>
+      <c r="M14" s="16"/>
+      <c r="N14" s="16"/>
+      <c r="O14" s="16"/>
+      <c r="P14" s="16"/>
+      <c r="Q14" s="16"/>
+      <c r="R14" s="16"/>
+      <c r="S14" s="16"/>
+      <c r="T14" s="16"/>
+      <c r="U14" s="16"/>
+      <c r="V14" s="16"/>
+      <c r="W14" s="16"/>
+      <c r="X14" s="16"/>
+      <c r="Y14" s="16"/>
+      <c r="Z14" s="16"/>
+      <c r="AA14" s="16"/>
+      <c r="AB14" s="16"/>
+      <c r="AC14" s="16"/>
+      <c r="AD14" s="16"/>
+      <c r="AE14" s="16"/>
+      <c r="AF14" s="16"/>
+      <c r="AG14" s="16"/>
+      <c r="AH14" s="16"/>
+      <c r="AI14" s="16"/>
+      <c r="AJ14" s="16"/>
+      <c r="AK14" s="16"/>
+      <c r="AL14" s="16"/>
+    </row>
+    <row r="15" spans="1:38" ht="15">
+      <c r="A15" s="15"/>
+      <c r="B15" s="12">
+        <v>2022</v>
+      </c>
+      <c r="C15" s="12">
+        <v>2023</v>
+      </c>
+      <c r="D15" s="12">
+        <v>2024</v>
+      </c>
+      <c r="E15" s="12">
+        <v>2025</v>
+      </c>
+      <c r="F15" s="12">
+        <v>2026</v>
+      </c>
+      <c r="G15" s="12">
+        <v>2027</v>
+      </c>
+      <c r="H15" s="12">
+        <v>2028</v>
+      </c>
+      <c r="I15" s="12">
+        <v>2029</v>
+      </c>
+      <c r="J15" s="12">
+        <v>2030</v>
+      </c>
+      <c r="K15" s="12">
+        <v>2031</v>
+      </c>
+      <c r="L15" s="12">
+        <v>2032</v>
+      </c>
+      <c r="M15" s="16"/>
+      <c r="N15" s="16"/>
+      <c r="O15" s="16"/>
+      <c r="P15" s="16"/>
+      <c r="Q15" s="16"/>
+      <c r="R15" s="16"/>
+      <c r="S15" s="16"/>
+      <c r="T15" s="16"/>
+      <c r="U15" s="16"/>
+      <c r="V15" s="16"/>
+      <c r="W15" s="16"/>
+      <c r="X15" s="16"/>
+      <c r="Y15" s="16"/>
+      <c r="Z15" s="16"/>
+      <c r="AA15" s="16"/>
+      <c r="AB15" s="16"/>
+      <c r="AC15" s="16"/>
+      <c r="AD15" s="16"/>
+      <c r="AE15" s="16"/>
+      <c r="AF15" s="16"/>
+      <c r="AG15" s="16"/>
+      <c r="AH15" s="16"/>
+      <c r="AI15" s="16"/>
+      <c r="AJ15" s="16"/>
+      <c r="AK15" s="16"/>
+      <c r="AL15" s="16"/>
+    </row>
+    <row r="16" spans="1:38" ht="15">
+      <c r="A16" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16" s="12"/>
+      <c r="C16" s="12">
+        <v>138</v>
+      </c>
+      <c r="D16" s="12">
+        <v>128</v>
+      </c>
+      <c r="E16" s="12">
+        <v>145</v>
+      </c>
+      <c r="F16" s="12">
+        <v>164</v>
+      </c>
+      <c r="G16" s="12">
+        <v>184</v>
+      </c>
+      <c r="H16" s="12">
+        <v>207</v>
+      </c>
+      <c r="I16" s="12">
+        <v>231</v>
+      </c>
+      <c r="J16" s="12">
+        <v>257</v>
+      </c>
+      <c r="K16" s="12">
+        <v>284</v>
+      </c>
+      <c r="L16" s="12"/>
+      <c r="M16" s="16"/>
+      <c r="N16" s="16"/>
+      <c r="O16" s="16"/>
+      <c r="P16" s="16"/>
+      <c r="Q16" s="16"/>
+      <c r="R16" s="16"/>
+      <c r="S16" s="16"/>
+      <c r="T16" s="16"/>
+      <c r="U16" s="16"/>
+      <c r="V16" s="16"/>
+      <c r="W16" s="16"/>
+      <c r="X16" s="16"/>
+      <c r="Y16" s="16"/>
+      <c r="Z16" s="16"/>
+      <c r="AA16" s="16"/>
+      <c r="AB16" s="16"/>
+      <c r="AC16" s="16"/>
+      <c r="AD16" s="16"/>
+      <c r="AE16" s="16"/>
+      <c r="AF16" s="16"/>
+      <c r="AG16" s="16"/>
+      <c r="AH16" s="16"/>
+      <c r="AI16" s="16"/>
+      <c r="AJ16" s="16"/>
+      <c r="AK16" s="16"/>
+      <c r="AL16" s="16"/>
+    </row>
+    <row r="17" spans="1:38" ht="15">
+      <c r="A17" s="12"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="12"/>
+      <c r="J17" s="12"/>
+      <c r="K17" s="12"/>
+      <c r="L17" s="12"/>
+      <c r="M17" s="16"/>
+      <c r="N17" s="16"/>
+      <c r="O17" s="16"/>
+      <c r="P17" s="16"/>
+      <c r="Q17" s="16"/>
+      <c r="R17" s="16"/>
+      <c r="S17" s="16"/>
+      <c r="T17" s="16"/>
+      <c r="U17" s="16"/>
+      <c r="V17" s="16"/>
+      <c r="W17" s="16"/>
+      <c r="X17" s="16"/>
+      <c r="Y17" s="16"/>
+      <c r="Z17" s="16"/>
+      <c r="AA17" s="16"/>
+      <c r="AB17" s="16"/>
+      <c r="AC17" s="16"/>
+      <c r="AD17" s="16"/>
+      <c r="AE17" s="16"/>
+      <c r="AF17" s="16"/>
+      <c r="AG17" s="16"/>
+      <c r="AH17" s="16"/>
+      <c r="AI17" s="16"/>
+      <c r="AJ17" s="16"/>
+      <c r="AK17" s="16"/>
+      <c r="AL17" s="16"/>
+    </row>
+    <row r="18" spans="1:38" ht="15">
+      <c r="A18" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" s="19">
+        <f>C16*0.925</f>
+        <v>127.65</v>
+      </c>
+      <c r="D18" s="19">
+        <f t="shared" ref="D18:L18" si="0">D16*0.925</f>
+        <v>118.4</v>
+      </c>
+      <c r="E18" s="19">
+        <f t="shared" si="0"/>
+        <v>134.125</v>
+      </c>
+      <c r="F18" s="19">
+        <f t="shared" si="0"/>
+        <v>151.70000000000002</v>
+      </c>
+      <c r="G18" s="19">
+        <f t="shared" si="0"/>
+        <v>170.20000000000002</v>
+      </c>
+      <c r="H18" s="19">
+        <f t="shared" si="0"/>
+        <v>191.47500000000002</v>
+      </c>
+      <c r="I18" s="19">
+        <f t="shared" si="0"/>
+        <v>213.67500000000001</v>
+      </c>
+      <c r="J18" s="19">
+        <f t="shared" si="0"/>
+        <v>237.72500000000002</v>
+      </c>
+      <c r="K18" s="19">
+        <f t="shared" si="0"/>
+        <v>262.7</v>
+      </c>
+      <c r="L18" s="19">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M18" s="16"/>
+      <c r="N18" s="16"/>
+      <c r="O18" s="16"/>
+      <c r="P18" s="16"/>
+      <c r="Q18" s="16"/>
+      <c r="R18" s="16"/>
+      <c r="S18" s="16"/>
+      <c r="T18" s="16"/>
+      <c r="U18" s="16"/>
+      <c r="V18" s="16"/>
+      <c r="W18" s="16"/>
+      <c r="X18" s="16"/>
+      <c r="Y18" s="16"/>
+      <c r="Z18" s="16"/>
+      <c r="AA18" s="16"/>
+      <c r="AB18" s="16"/>
+      <c r="AC18" s="16"/>
+      <c r="AD18" s="16"/>
+      <c r="AE18" s="16"/>
+      <c r="AF18" s="16"/>
+      <c r="AG18" s="16"/>
+      <c r="AH18" s="16"/>
+      <c r="AI18" s="16"/>
+      <c r="AJ18" s="16"/>
+      <c r="AK18" s="16"/>
+      <c r="AL18" s="16"/>
+    </row>
+    <row r="19" spans="1:38" ht="15">
+      <c r="A19" s="15"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="15"/>
+      <c r="H19" s="15"/>
+      <c r="I19" s="15"/>
+      <c r="J19" s="15"/>
+      <c r="K19" s="15"/>
+      <c r="L19" s="15"/>
+      <c r="M19" s="16"/>
+      <c r="N19" s="16"/>
+      <c r="O19" s="16"/>
+      <c r="P19" s="16"/>
+      <c r="Q19" s="16"/>
+      <c r="R19" s="16"/>
+      <c r="S19" s="16"/>
+      <c r="T19" s="16"/>
+      <c r="U19" s="16"/>
+      <c r="V19" s="16"/>
+      <c r="W19" s="16"/>
+      <c r="X19" s="16"/>
+      <c r="Y19" s="16"/>
+      <c r="Z19" s="16"/>
+      <c r="AA19" s="16"/>
+      <c r="AB19" s="16"/>
+      <c r="AC19" s="16"/>
+      <c r="AD19" s="16"/>
+      <c r="AE19" s="16"/>
+      <c r="AF19" s="16"/>
+      <c r="AG19" s="16"/>
+      <c r="AH19" s="16"/>
+      <c r="AI19" s="16"/>
+      <c r="AJ19" s="16"/>
+      <c r="AK19" s="16"/>
+      <c r="AL19" s="16"/>
+    </row>
+    <row r="20" spans="1:38" ht="15">
+      <c r="B20" s="12">
+        <v>2022</v>
+      </c>
+      <c r="C20" s="12">
+        <v>2023</v>
+      </c>
+      <c r="D20" s="12">
+        <v>2024</v>
+      </c>
+      <c r="E20" s="12">
+        <v>2025</v>
+      </c>
+      <c r="F20" s="12">
+        <v>2026</v>
+      </c>
+      <c r="G20" s="12">
+        <v>2027</v>
+      </c>
+      <c r="H20" s="12">
+        <v>2028</v>
+      </c>
+      <c r="I20" s="12">
+        <v>2029</v>
+      </c>
+      <c r="J20" s="12">
+        <v>2030</v>
+      </c>
+      <c r="K20" s="12">
+        <v>2031</v>
+      </c>
+      <c r="L20" s="12">
+        <v>2032</v>
+      </c>
+      <c r="M20" s="16"/>
+      <c r="N20" s="16"/>
+      <c r="O20" s="16"/>
+      <c r="P20" s="16"/>
+      <c r="Q20" s="16"/>
+      <c r="R20" s="16"/>
+      <c r="S20" s="16"/>
+      <c r="T20" s="16"/>
+      <c r="U20" s="16"/>
+      <c r="V20" s="16"/>
+      <c r="W20" s="16"/>
+      <c r="X20" s="16"/>
+      <c r="Y20" s="16"/>
+      <c r="Z20" s="16"/>
+      <c r="AA20" s="16"/>
+      <c r="AB20" s="16"/>
+      <c r="AC20" s="16"/>
+      <c r="AD20" s="16"/>
+      <c r="AE20" s="16"/>
+      <c r="AF20" s="16"/>
+      <c r="AG20" s="16"/>
+      <c r="AH20" s="16"/>
+      <c r="AI20" s="16"/>
+      <c r="AJ20" s="16"/>
+      <c r="AK20" s="16"/>
+      <c r="AL20" s="16"/>
+    </row>
+    <row r="21" spans="1:38" ht="15">
+      <c r="A21" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" s="12">
+        <v>0</v>
+      </c>
+      <c r="C21" s="19">
+        <f>(C18*10^6)/$B$10/($B$7/$B$8)*$B$12</f>
+        <v>10932.127807552264</v>
+      </c>
+      <c r="D21" s="19">
+        <f t="shared" ref="D21:K21" si="1">(D18*10^6)/$B$10/($B$7/$B$8)*$B$12</f>
+        <v>10139.944633091956</v>
+      </c>
+      <c r="E21" s="19">
+        <f t="shared" si="1"/>
+        <v>11486.656029674483</v>
+      </c>
+      <c r="F21" s="19">
+        <f t="shared" si="1"/>
+        <v>12991.804061149072</v>
+      </c>
+      <c r="G21" s="19">
+        <f t="shared" si="1"/>
+        <v>14576.17041006969</v>
+      </c>
+      <c r="H21" s="19">
+        <f t="shared" si="1"/>
+        <v>16398.1917113284</v>
+      </c>
+      <c r="I21" s="19">
+        <f t="shared" si="1"/>
+        <v>18299.431330033138</v>
+      </c>
+      <c r="J21" s="19">
+        <f t="shared" si="1"/>
+        <v>20359.107583629942</v>
+      </c>
+      <c r="K21" s="19">
+        <f t="shared" si="1"/>
+        <v>22498.00215467278</v>
+      </c>
+      <c r="L21" s="19">
+        <f>(L18*10^6)/$B$10/$B$7*$B$12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:38" ht="15">
+      <c r="A22" s="15"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="15"/>
+      <c r="I22" s="15"/>
+      <c r="J22" s="15"/>
+      <c r="K22" s="15"/>
+      <c r="L22" s="15"/>
+      <c r="M22" s="16"/>
+      <c r="N22" s="16"/>
+      <c r="O22" s="16"/>
+      <c r="P22" s="16"/>
+      <c r="Q22" s="16"/>
+      <c r="R22" s="16"/>
+      <c r="S22" s="16"/>
+      <c r="T22" s="16"/>
+      <c r="U22" s="16"/>
+      <c r="V22" s="16"/>
+      <c r="W22" s="16"/>
+      <c r="X22" s="16"/>
+      <c r="Y22" s="16"/>
+      <c r="Z22" s="16"/>
+      <c r="AA22" s="16"/>
+      <c r="AB22" s="16"/>
+      <c r="AC22" s="16"/>
+      <c r="AD22" s="16"/>
+      <c r="AE22" s="16"/>
+      <c r="AF22" s="16"/>
+      <c r="AG22" s="16"/>
+      <c r="AH22" s="16"/>
+      <c r="AI22" s="16"/>
+      <c r="AJ22" s="16"/>
+      <c r="AK22" s="16"/>
+      <c r="AL22" s="16"/>
+    </row>
+    <row r="23" spans="1:38" ht="15">
+      <c r="A23" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" s="19">
+        <f>SUM(C21:K21)</f>
+        <v>137681.43572120171</v>
+      </c>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="12"/>
+      <c r="J23" s="12"/>
+      <c r="K23" s="12"/>
+      <c r="L23" s="12"/>
+    </row>
+    <row r="24" spans="1:38" ht="15">
+      <c r="A24" s="15"/>
+      <c r="B24" s="15"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="15"/>
+      <c r="H24" s="15"/>
+      <c r="I24" s="15"/>
+      <c r="J24" s="15"/>
+      <c r="K24" s="15"/>
+      <c r="L24" s="15"/>
+      <c r="M24" s="16"/>
+      <c r="N24" s="16"/>
+      <c r="O24" s="16"/>
+      <c r="P24" s="16"/>
+      <c r="Q24" s="16"/>
+      <c r="R24" s="16"/>
+      <c r="S24" s="16"/>
+      <c r="T24" s="16"/>
+      <c r="U24" s="16"/>
+      <c r="V24" s="16"/>
+      <c r="W24" s="16"/>
+      <c r="X24" s="16"/>
+      <c r="Y24" s="16"/>
+      <c r="Z24" s="16"/>
+      <c r="AA24" s="16"/>
+      <c r="AB24" s="16"/>
+      <c r="AC24" s="16"/>
+      <c r="AD24" s="16"/>
+      <c r="AE24" s="16"/>
+      <c r="AF24" s="16"/>
+      <c r="AG24" s="16"/>
+      <c r="AH24" s="16"/>
+      <c r="AI24" s="16"/>
+      <c r="AJ24" s="16"/>
+      <c r="AK24" s="16"/>
+      <c r="AL24" s="16"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A4" r:id="rId1" display="Source: https://www.democrats.senate.gov/imo/media/doc/21-2093.pdf" xr:uid="{30969EEE-E72F-4B62-81B5-E66A5CDAAD8E}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{341A17B3-AFD9-42DA-AB68-E46FC6CF1D40}">
+  <dimension ref="A1:AF11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="45.140625" customWidth="1"/>
+    <col min="2" max="2" width="26.42578125" customWidth="1"/>
+    <col min="3" max="4" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:32">
+      <c r="A1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1">
+        <v>1200000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32">
+      <c r="A3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32">
+      <c r="A4">
+        <v>2022</v>
+      </c>
+      <c r="B4">
+        <v>137902</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32">
+      <c r="A5">
+        <v>2050</v>
+      </c>
+      <c r="B5">
+        <v>1200000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32">
+      <c r="B7">
+        <v>2020</v>
+      </c>
+      <c r="C7">
+        <v>2021</v>
+      </c>
+      <c r="D7">
+        <v>2022</v>
+      </c>
+      <c r="E7">
+        <v>2023</v>
+      </c>
+      <c r="F7">
+        <v>2024</v>
+      </c>
+      <c r="G7">
+        <v>2025</v>
+      </c>
+      <c r="H7">
+        <v>2026</v>
+      </c>
+      <c r="I7">
+        <v>2027</v>
+      </c>
+      <c r="J7">
+        <v>2028</v>
+      </c>
+      <c r="K7">
+        <v>2029</v>
+      </c>
+      <c r="L7">
+        <v>2030</v>
+      </c>
+      <c r="M7">
+        <v>2031</v>
+      </c>
+      <c r="N7">
+        <v>2032</v>
+      </c>
+      <c r="O7">
+        <v>2033</v>
+      </c>
+      <c r="P7">
+        <v>2034</v>
+      </c>
+      <c r="Q7">
+        <v>2035</v>
+      </c>
+      <c r="R7">
+        <v>2036</v>
+      </c>
+      <c r="S7">
+        <v>2037</v>
+      </c>
+      <c r="T7">
+        <v>2038</v>
+      </c>
+      <c r="U7">
+        <v>2039</v>
+      </c>
+      <c r="V7">
+        <v>2040</v>
+      </c>
+      <c r="W7">
+        <v>2041</v>
+      </c>
+      <c r="X7">
+        <v>2042</v>
+      </c>
+      <c r="Y7">
+        <v>2043</v>
+      </c>
+      <c r="Z7">
+        <v>2044</v>
+      </c>
+      <c r="AA7">
+        <v>2045</v>
+      </c>
+      <c r="AB7">
+        <v>2046</v>
+      </c>
+      <c r="AC7">
+        <v>2047</v>
+      </c>
+      <c r="AD7">
+        <v>2048</v>
+      </c>
+      <c r="AE7">
+        <v>2049</v>
+      </c>
+      <c r="AF7">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32">
+      <c r="A8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8">
+        <f>D8</f>
+        <v>137902</v>
+      </c>
+      <c r="C8">
+        <f>D8</f>
+        <v>137902</v>
+      </c>
+      <c r="D8" cm="1">
+        <f t="array" ref="D8">TREND($B$4:$B$5,$A$4:$A$5,D7)</f>
+        <v>137902</v>
+      </c>
+      <c r="E8" cm="1">
+        <f t="array" ref="E8">TREND($B$4:$B$5,$A$4:$A$5,E7)</f>
+        <v>175834.07142856717</v>
+      </c>
+      <c r="F8" cm="1">
+        <f t="array" ref="F8">TREND($B$4:$B$5,$A$4:$A$5,F7)</f>
+        <v>213766.14285713434</v>
+      </c>
+      <c r="G8" cm="1">
+        <f t="array" ref="G8">TREND($B$4:$B$5,$A$4:$A$5,G7)</f>
+        <v>251698.21428570151</v>
+      </c>
+      <c r="H8" cm="1">
+        <f t="array" ref="H8">TREND($B$4:$B$5,$A$4:$A$5,H7)</f>
+        <v>289630.28571428359</v>
+      </c>
+      <c r="I8" cm="1">
+        <f t="array" ref="I8">TREND($B$4:$B$5,$A$4:$A$5,I7)</f>
+        <v>327562.35714285076</v>
+      </c>
+      <c r="J8" cm="1">
+        <f t="array" ref="J8">TREND($B$4:$B$5,$A$4:$A$5,J7)</f>
+        <v>365494.42857141793</v>
+      </c>
+      <c r="K8" cm="1">
+        <f t="array" ref="K8">TREND($B$4:$B$5,$A$4:$A$5,K7)</f>
+        <v>403426.5</v>
+      </c>
+      <c r="L8" cm="1">
+        <f t="array" ref="L8">TREND($B$4:$B$5,$A$4:$A$5,L7)</f>
+        <v>441358.57142856717</v>
+      </c>
+      <c r="M8" cm="1">
+        <f t="array" ref="M8">TREND($B$4:$B$5,$A$4:$A$5,M7)</f>
+        <v>479290.64285713434</v>
+      </c>
+      <c r="N8" cm="1">
+        <f t="array" ref="N8">TREND($B$4:$B$5,$A$4:$A$5,N7)</f>
+        <v>517222.71428570151</v>
+      </c>
+      <c r="O8" cm="1">
+        <f t="array" ref="O8">TREND($B$4:$B$5,$A$4:$A$5,O7)</f>
+        <v>555154.78571428359</v>
+      </c>
+      <c r="P8" cm="1">
+        <f t="array" ref="P8">TREND($B$4:$B$5,$A$4:$A$5,P7)</f>
+        <v>593086.85714285076</v>
+      </c>
+      <c r="Q8" cm="1">
+        <f t="array" ref="Q8">TREND($B$4:$B$5,$A$4:$A$5,Q7)</f>
+        <v>631018.92857141793</v>
+      </c>
+      <c r="R8" cm="1">
+        <f t="array" ref="R8">TREND($B$4:$B$5,$A$4:$A$5,R7)</f>
+        <v>668951</v>
+      </c>
+      <c r="S8" cm="1">
+        <f t="array" ref="S8">TREND($B$4:$B$5,$A$4:$A$5,S7)</f>
+        <v>706883.07142856717</v>
+      </c>
+      <c r="T8" cm="1">
+        <f t="array" ref="T8">TREND($B$4:$B$5,$A$4:$A$5,T7)</f>
+        <v>744815.14285713434</v>
+      </c>
+      <c r="U8" cm="1">
+        <f t="array" ref="U8">TREND($B$4:$B$5,$A$4:$A$5,U7)</f>
+        <v>782747.21428570151</v>
+      </c>
+      <c r="V8" cm="1">
+        <f t="array" ref="V8">TREND($B$4:$B$5,$A$4:$A$5,V7)</f>
+        <v>820679.28571428359</v>
+      </c>
+      <c r="W8" cm="1">
+        <f t="array" ref="W8">TREND($B$4:$B$5,$A$4:$A$5,W7)</f>
+        <v>858611.35714285076</v>
+      </c>
+      <c r="X8" cm="1">
+        <f t="array" ref="X8">TREND($B$4:$B$5,$A$4:$A$5,X7)</f>
+        <v>896543.42857141793</v>
+      </c>
+      <c r="Y8" cm="1">
+        <f t="array" ref="Y8">TREND($B$4:$B$5,$A$4:$A$5,Y7)</f>
+        <v>934475.5</v>
+      </c>
+      <c r="Z8" cm="1">
+        <f t="array" ref="Z8">TREND($B$4:$B$5,$A$4:$A$5,Z7)</f>
+        <v>972407.57142856717</v>
+      </c>
+      <c r="AA8" cm="1">
+        <f t="array" ref="AA8">TREND($B$4:$B$5,$A$4:$A$5,AA7)</f>
+        <v>1010339.6428571343</v>
+      </c>
+      <c r="AB8" cm="1">
+        <f t="array" ref="AB8">TREND($B$4:$B$5,$A$4:$A$5,AB7)</f>
+        <v>1048271.7142857015</v>
+      </c>
+      <c r="AC8" cm="1">
+        <f t="array" ref="AC8">TREND($B$4:$B$5,$A$4:$A$5,AC7)</f>
+        <v>1086203.7857142836</v>
+      </c>
+      <c r="AD8" cm="1">
+        <f t="array" ref="AD8">TREND($B$4:$B$5,$A$4:$A$5,AD7)</f>
+        <v>1124135.8571428508</v>
+      </c>
+      <c r="AE8" cm="1">
+        <f t="array" ref="AE8">TREND($B$4:$B$5,$A$4:$A$5,AE7)</f>
+        <v>1162067.9285714179</v>
+      </c>
+      <c r="AF8" cm="1">
+        <f t="array" ref="AF8">TREND($B$4:$B$5,$A$4:$A$5,AF7)</f>
+        <v>1200000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32">
+      <c r="A9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="E9" s="2">
+        <f>IIJA!$B$10</f>
+        <v>64995.918791303513</v>
+      </c>
+      <c r="F9" s="2">
+        <f>IIJA!$B$10</f>
+        <v>64995.918791303513</v>
+      </c>
+      <c r="G9" s="2">
+        <f>IIJA!$B$10</f>
+        <v>64995.918791303513</v>
+      </c>
+      <c r="H9" s="2">
+        <f>IIJA!$B$10</f>
+        <v>64995.918791303513</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>0</v>
+      </c>
+      <c r="Y9">
+        <v>0</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0</v>
+      </c>
+      <c r="AC9">
+        <v>0</v>
+      </c>
+      <c r="AD9">
+        <v>0</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10" s="2">
+        <f>'Inflation Reduction Act'!C21</f>
+        <v>10932.127807552264</v>
+      </c>
+      <c r="F10" s="2">
+        <f>'Inflation Reduction Act'!D21</f>
+        <v>10139.944633091956</v>
+      </c>
+      <c r="G10" s="2">
+        <f>'Inflation Reduction Act'!E21</f>
+        <v>11486.656029674483</v>
+      </c>
+      <c r="H10" s="2">
+        <f>'Inflation Reduction Act'!F21</f>
+        <v>12991.804061149072</v>
+      </c>
+      <c r="I10" s="2">
+        <f>'Inflation Reduction Act'!G21</f>
+        <v>14576.17041006969</v>
+      </c>
+      <c r="J10" s="2">
+        <f>'Inflation Reduction Act'!H21</f>
+        <v>16398.1917113284</v>
+      </c>
+      <c r="K10" s="2">
+        <f>'Inflation Reduction Act'!I21</f>
+        <v>18299.431330033138</v>
+      </c>
+      <c r="L10" s="2">
+        <f>'Inflation Reduction Act'!J21</f>
+        <v>20359.107583629942</v>
+      </c>
+      <c r="M10" s="2">
+        <f>'Inflation Reduction Act'!K21</f>
+        <v>22498.00215467278</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>0</v>
+      </c>
+      <c r="Y10">
+        <v>0</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0</v>
+      </c>
+      <c r="AC10">
+        <v>0</v>
+      </c>
+      <c r="AD10">
+        <v>0</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32">
+      <c r="A11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11">
+        <f>SUM(B8:B10)</f>
+        <v>137902</v>
+      </c>
+      <c r="C11">
+        <f>SUM(C8:C10)</f>
+        <v>137902</v>
+      </c>
+      <c r="D11">
+        <f>C11+(D8-C8)+SUM(D9:D10)</f>
+        <v>137902</v>
+      </c>
+      <c r="E11">
+        <f t="shared" ref="E11:AF11" si="0">D11+(E8-D8)+SUM(E9:E10)</f>
+        <v>251762.11802742296</v>
+      </c>
+      <c r="F11">
+        <f t="shared" si="0"/>
+        <v>364830.05288038554</v>
+      </c>
+      <c r="G11">
+        <f t="shared" si="0"/>
+        <v>479244.6991299307</v>
+      </c>
+      <c r="H11">
+        <f t="shared" si="0"/>
+        <v>595164.49341096531</v>
+      </c>
+      <c r="I11">
+        <f t="shared" si="0"/>
+        <v>647672.73524960212</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="0"/>
+        <v>702002.99838949763</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="0"/>
+        <v>758234.50114811282</v>
+      </c>
+      <c r="L11">
+        <f t="shared" si="0"/>
+        <v>816525.68016030989</v>
+      </c>
+      <c r="M11">
+        <f t="shared" si="0"/>
+        <v>876955.75374354981</v>
+      </c>
+      <c r="N11">
+        <f t="shared" si="0"/>
+        <v>914887.82517211698</v>
+      </c>
+      <c r="O11">
+        <f t="shared" si="0"/>
+        <v>952819.89660069905</v>
+      </c>
+      <c r="P11">
+        <f t="shared" si="0"/>
+        <v>990751.96802926622</v>
+      </c>
+      <c r="Q11">
+        <f t="shared" si="0"/>
+        <v>1028684.0394578334</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="0"/>
+        <v>1066616.1108864155</v>
+      </c>
+      <c r="S11">
+        <f t="shared" si="0"/>
+        <v>1104548.1823149826</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="0"/>
+        <v>1142480.2537435498</v>
+      </c>
+      <c r="U11">
+        <f t="shared" si="0"/>
+        <v>1180412.325172117</v>
+      </c>
+      <c r="V11">
+        <f t="shared" si="0"/>
+        <v>1218344.3966006991</v>
+      </c>
+      <c r="W11">
+        <f t="shared" si="0"/>
+        <v>1256276.4680292662</v>
+      </c>
+      <c r="X11">
+        <f t="shared" si="0"/>
+        <v>1294208.5394578334</v>
+      </c>
+      <c r="Y11">
+        <f t="shared" si="0"/>
+        <v>1332140.6108864155</v>
+      </c>
+      <c r="Z11">
+        <f t="shared" si="0"/>
+        <v>1370072.6823149826</v>
+      </c>
+      <c r="AA11">
+        <f t="shared" si="0"/>
+        <v>1408004.7537435498</v>
+      </c>
+      <c r="AB11">
+        <f t="shared" si="0"/>
+        <v>1445936.825172117</v>
+      </c>
+      <c r="AC11">
+        <f t="shared" si="0"/>
+        <v>1483868.8966006991</v>
+      </c>
+      <c r="AD11">
+        <f t="shared" si="0"/>
+        <v>1521800.9680292662</v>
+      </c>
+      <c r="AE11">
+        <f t="shared" si="0"/>
+        <v>1559733.0394578334</v>
+      </c>
+      <c r="AF11">
+        <f t="shared" si="0"/>
+        <v>1597665.1108864155</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AC2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AF2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:32">
       <c r="A1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="3">
+        <v>32</v>
+      </c>
+      <c r="B1">
+        <v>2021</v>
+      </c>
+      <c r="C1" s="3">
+        <v>2022</v>
+      </c>
+      <c r="D1">
+        <v>2023</v>
+      </c>
+      <c r="E1" s="3">
         <v>2024</v>
       </c>
-      <c r="C1">
+      <c r="F1">
         <v>2025</v>
       </c>
-      <c r="D1" s="3">
+      <c r="G1" s="3">
         <v>2026</v>
       </c>
-      <c r="E1">
+      <c r="H1">
         <v>2027</v>
       </c>
-      <c r="F1" s="3">
+      <c r="I1" s="3">
         <v>2028</v>
       </c>
-      <c r="G1">
+      <c r="J1">
         <v>2029</v>
       </c>
-      <c r="H1" s="3">
+      <c r="K1" s="3">
         <v>2030</v>
       </c>
-      <c r="I1">
+      <c r="L1">
         <v>2031</v>
       </c>
-      <c r="J1" s="3">
+      <c r="M1" s="3">
         <v>2032</v>
       </c>
-      <c r="K1">
+      <c r="N1">
         <v>2033</v>
       </c>
-      <c r="L1" s="3">
+      <c r="O1" s="3">
         <v>2034</v>
       </c>
-      <c r="M1">
+      <c r="P1">
         <v>2035</v>
       </c>
-      <c r="N1" s="3">
+      <c r="Q1" s="3">
         <v>2036</v>
       </c>
-      <c r="O1">
+      <c r="R1">
         <v>2037</v>
       </c>
-      <c r="P1" s="3">
+      <c r="S1" s="3">
         <v>2038</v>
       </c>
-      <c r="Q1">
+      <c r="T1">
         <v>2039</v>
       </c>
-      <c r="R1" s="3">
+      <c r="U1" s="3">
         <v>2040</v>
       </c>
-      <c r="S1">
+      <c r="V1">
         <v>2041</v>
       </c>
-      <c r="T1" s="3">
+      <c r="W1" s="3">
         <v>2042</v>
       </c>
-      <c r="U1">
+      <c r="X1">
         <v>2043</v>
       </c>
-      <c r="V1" s="3">
+      <c r="Y1" s="3">
         <v>2044</v>
       </c>
-      <c r="W1">
+      <c r="Z1">
         <v>2045</v>
       </c>
-      <c r="X1" s="3">
+      <c r="AA1" s="3">
         <v>2046</v>
       </c>
-      <c r="Y1">
+      <c r="AB1">
         <v>2047</v>
       </c>
-      <c r="Z1" s="3">
+      <c r="AC1" s="3">
         <v>2048</v>
       </c>
-      <c r="AA1">
+      <c r="AD1">
         <v>2049</v>
       </c>
-      <c r="AB1" s="3">
+      <c r="AE1" s="3">
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:32">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="B2" s="2">
-        <f>144823+49604</f>
-        <v>194427</v>
+        <f>Calculations!C11</f>
+        <v>137902</v>
       </c>
       <c r="C2" s="2">
-        <f>170010+66374</f>
-        <v>236384</v>
-      </c>
-      <c r="D2" cm="1">
-        <f t="array" ref="D2">TREND($B$2:$C$2,$B$1:$C$1,D1)</f>
-        <v>278341</v>
-      </c>
-      <c r="E2" cm="1">
-        <f t="array" ref="E2">TREND($B$2:$C$2,$B$1:$C$1,E1)</f>
-        <v>320298</v>
-      </c>
-      <c r="F2" cm="1">
-        <f t="array" ref="F2">TREND($B$2:$C$2,$B$1:$C$1,F1)</f>
-        <v>362255</v>
-      </c>
-      <c r="G2" cm="1">
-        <f t="array" ref="G2">TREND($B$2:$C$2,$B$1:$C$1,G1)</f>
-        <v>404212</v>
-      </c>
-      <c r="H2" cm="1">
-        <f t="array" ref="H2">TREND($B$2:$C$2,$B$1:$C$1,H1)</f>
-        <v>446169</v>
-      </c>
-      <c r="I2" cm="1">
-        <f t="array" ref="I2">TREND($B$2:$C$2,$B$1:$C$1,I1)</f>
-        <v>488126</v>
-      </c>
-      <c r="J2" cm="1">
-        <f t="array" ref="J2">TREND($B$2:$C$2,$B$1:$C$1,J1)</f>
-        <v>530083</v>
-      </c>
-      <c r="K2" cm="1">
-        <f t="array" ref="K2">TREND($B$2:$C$2,$B$1:$C$1,K1)</f>
-        <v>572040</v>
-      </c>
-      <c r="L2" cm="1">
-        <f t="array" ref="L2">TREND($B$2:$C$2,$B$1:$C$1,L1)</f>
-        <v>613997</v>
-      </c>
-      <c r="M2" cm="1">
-        <f t="array" ref="M2">TREND($B$2:$C$2,$B$1:$C$1,M1)</f>
-        <v>655954</v>
-      </c>
-      <c r="N2" cm="1">
-        <f t="array" ref="N2">TREND($B$2:$C$2,$B$1:$C$1,N1)</f>
-        <v>697911</v>
-      </c>
-      <c r="O2" cm="1">
-        <f t="array" ref="O2">TREND($B$2:$C$2,$B$1:$C$1,O1)</f>
-        <v>739868</v>
-      </c>
-      <c r="P2" cm="1">
-        <f t="array" ref="P2">TREND($B$2:$C$2,$B$1:$C$1,P1)</f>
-        <v>781825</v>
-      </c>
-      <c r="Q2" cm="1">
-        <f t="array" ref="Q2">TREND($B$2:$C$2,$B$1:$C$1,Q1)</f>
-        <v>823782</v>
-      </c>
-      <c r="R2" cm="1">
-        <f t="array" ref="R2">TREND($B$2:$C$2,$B$1:$C$1,R1)</f>
-        <v>865739</v>
-      </c>
-      <c r="S2" cm="1">
-        <f t="array" ref="S2">TREND($B$2:$C$2,$B$1:$C$1,S1)</f>
-        <v>907696</v>
-      </c>
-      <c r="T2" cm="1">
-        <f t="array" ref="T2">TREND($B$2:$C$2,$B$1:$C$1,T1)</f>
-        <v>949653</v>
-      </c>
-      <c r="U2" cm="1">
-        <f t="array" ref="U2">TREND($B$2:$C$2,$B$1:$C$1,U1)</f>
-        <v>991610</v>
-      </c>
-      <c r="V2" cm="1">
-        <f t="array" ref="V2">TREND($B$2:$C$2,$B$1:$C$1,V1)</f>
-        <v>1033567</v>
-      </c>
-      <c r="W2" cm="1">
-        <f t="array" ref="W2">TREND($B$2:$C$2,$B$1:$C$1,W1)</f>
-        <v>1075524</v>
-      </c>
-      <c r="X2" cm="1">
-        <f t="array" ref="X2">TREND($B$2:$C$2,$B$1:$C$1,X1)</f>
-        <v>1117481</v>
-      </c>
-      <c r="Y2" cm="1">
-        <f t="array" ref="Y2">TREND($B$2:$C$2,$B$1:$C$1,Y1)</f>
-        <v>1159438</v>
-      </c>
-      <c r="Z2" cm="1">
-        <f t="array" ref="Z2">TREND($B$2:$C$2,$B$1:$C$1,Z1)</f>
-        <v>1201395</v>
-      </c>
-      <c r="AA2" cm="1">
-        <f t="array" ref="AA2">TREND($B$2:$C$2,$B$1:$C$1,AA1)</f>
-        <v>1243352</v>
-      </c>
-      <c r="AB2" cm="1">
-        <f t="array" ref="AB2">TREND($B$2:$C$2,$B$1:$C$1,AB1)</f>
-        <v>1285309</v>
-      </c>
-      <c r="AC2" s="2"/>
+        <f>Calculations!D11</f>
+        <v>137902</v>
+      </c>
+      <c r="D2" s="2">
+        <f>Calculations!E11</f>
+        <v>251762.11802742296</v>
+      </c>
+      <c r="E2" s="2">
+        <f>Calculations!F11</f>
+        <v>364830.05288038554</v>
+      </c>
+      <c r="F2" s="2">
+        <f>Calculations!G11</f>
+        <v>479244.6991299307</v>
+      </c>
+      <c r="G2" s="2">
+        <f>Calculations!H11</f>
+        <v>595164.49341096531</v>
+      </c>
+      <c r="H2" s="2">
+        <f>Calculations!I11</f>
+        <v>647672.73524960212</v>
+      </c>
+      <c r="I2" s="2">
+        <f>Calculations!J11</f>
+        <v>702002.99838949763</v>
+      </c>
+      <c r="J2" s="2">
+        <f>Calculations!K11</f>
+        <v>758234.50114811282</v>
+      </c>
+      <c r="K2" s="2">
+        <f>Calculations!L11</f>
+        <v>816525.68016030989</v>
+      </c>
+      <c r="L2" s="2">
+        <f>Calculations!M11</f>
+        <v>876955.75374354981</v>
+      </c>
+      <c r="M2" s="2">
+        <f>Calculations!N11</f>
+        <v>914887.82517211698</v>
+      </c>
+      <c r="N2" s="2">
+        <f>Calculations!O11</f>
+        <v>952819.89660069905</v>
+      </c>
+      <c r="O2" s="2">
+        <f>Calculations!P11</f>
+        <v>990751.96802926622</v>
+      </c>
+      <c r="P2" s="2">
+        <f>Calculations!Q11</f>
+        <v>1028684.0394578334</v>
+      </c>
+      <c r="Q2" s="2">
+        <f>Calculations!R11</f>
+        <v>1066616.1108864155</v>
+      </c>
+      <c r="R2" s="2">
+        <f>Calculations!S11</f>
+        <v>1104548.1823149826</v>
+      </c>
+      <c r="S2" s="2">
+        <f>Calculations!T11</f>
+        <v>1142480.2537435498</v>
+      </c>
+      <c r="T2" s="2">
+        <f>Calculations!U11</f>
+        <v>1180412.325172117</v>
+      </c>
+      <c r="U2" s="2">
+        <f>Calculations!V11</f>
+        <v>1218344.3966006991</v>
+      </c>
+      <c r="V2" s="2">
+        <f>Calculations!W11</f>
+        <v>1256276.4680292662</v>
+      </c>
+      <c r="W2" s="2">
+        <f>Calculations!X11</f>
+        <v>1294208.5394578334</v>
+      </c>
+      <c r="X2" s="2">
+        <f>Calculations!Y11</f>
+        <v>1332140.6108864155</v>
+      </c>
+      <c r="Y2" s="2">
+        <f>Calculations!Z11</f>
+        <v>1370072.6823149826</v>
+      </c>
+      <c r="Z2" s="2">
+        <f>Calculations!AA11</f>
+        <v>1408004.7537435498</v>
+      </c>
+      <c r="AA2" s="2">
+        <f>Calculations!AB11</f>
+        <v>1445936.825172117</v>
+      </c>
+      <c r="AB2" s="2">
+        <f>Calculations!AC11</f>
+        <v>1483868.8966006991</v>
+      </c>
+      <c r="AC2" s="2">
+        <f>Calculations!AD11</f>
+        <v>1521800.9680292662</v>
+      </c>
+      <c r="AD2" s="2">
+        <f>Calculations!AE11</f>
+        <v>1559733.0394578334</v>
+      </c>
+      <c r="AE2" s="2">
+        <f>Calculations!AF11</f>
+        <v>1597665.1108864155</v>
+      </c>
+      <c r="AF2" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
